--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM5"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,12 +883,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30030290-EBP</t>
+          <t>30035089-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30030290;2027,AP,Mercedes-Benz,EU V530-IP, welding, 250266, T,Equipment</t>
+          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -904,7 +904,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>SAIC-GM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -914,15 +914,19 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Min Hongen_闵宏恩(uminh009)</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -930,7 +934,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 1 Quotation</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -944,26 +948,26 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" s="1" t="n">
-        <v>45906</v>
+        <v>46151</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" s="1" t="n">
-        <v>45920</v>
+        <v>46158</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" s="1" t="n">
-        <v>45981</v>
+        <v>46165</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" s="1" t="n">
-        <v>46142</v>
+        <v>46186</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2027-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -971,10 +975,408 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Total,0
+Wang Hao23,0
+Lu Dinghao,100
+Xu Shirong,0
+Zhao Kailiang,0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Total,0
+Wang Hao23,0
+Xu Shirong,0
+Zhao Kailiang,0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>未确认(cao liang)</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30034747-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Cheng Debao_程德宝(uched025)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Total,0
+Wang Hao23,0
+Lu Dinghao,100
+Lu Gongchao,0
+Xu Shirong,0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Total,0
+Wang Hao23,0
+Lu Gongchao,0
+Xu Shirong,0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>未确认(cao liang)</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30034624-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30034624-2026,AP,BYD,Lamination,260102,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Total,0
+Wang Hao23,0
+Lu Dinghao,100
+Lu Gongchao,0
+Xu Shirong,0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Total,0
+Wang Hao23,0
+Lu Gongchao,0
+Xu Shirong,0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>未确认(cao liang)</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30030290-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30030290-2027,AP,Mercedes-Benz,EU V530-IP, welding, 250266, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Min Hongen_闵宏恩(uminh009)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" s="1" t="n">
+        <v>45906</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" s="1" t="n">
+        <v>45920</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>Total,0
 Tao Qichen,0
@@ -984,7 +1386,7 @@
 Zhao Kailiang,0</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>Total,0
 Tao Qichen,0
@@ -992,7 +1394,7 @@
 Zhao Kailiang,0</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Total,Submitted
 Tao Qichen,style="color:
@@ -1002,109 +1404,111 @@
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>未确认(cao liang)</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>30030289-EBP</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30030289;2027,AP,Mercedes-Benz,EU V530-IP, welding, 250265, T,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30030289-2027,AP,Mercedes-Benz,EU V530-IP, welding, 250265, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>DFM</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Mercedes-Benz</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Fan Jiejie_樊皆杰(ufanj028)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Gao Yiheng01_高一恒(ugaoy160)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" s="1" t="n">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" s="1" t="n">
         <v>45906</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" s="1" t="n">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" s="1" t="n">
         <v>45920</v>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" s="1" t="n">
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="AC5" t="inlineStr">
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>2027-09-30</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>Total,0
 Tao Qichen,100
@@ -1114,14 +1518,14 @@
 Zhao Kailiang,0</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>Total,0
 Xu Shirong,0
 Zhao Kailiang,0</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>Total,Submitted
 Tao Qichen,Submitted
@@ -1131,13 +1535,15 @@
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>未确认(cao liang)</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -983,7 +983,7 @@
           <t>Total,0
 Wang Hao23,0
 Lu Dinghao,100
-Xu Shirong,0
+Xu Shirong,100
 Zhao Kailiang,0</t>
         </is>
       </c>
@@ -991,7 +991,6 @@
         <is>
           <t>Total,0
 Wang Hao23,0
-Xu Shirong,0
 Zhao Kailiang,0</t>
         </is>
       </c>
@@ -1000,7 +999,7 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -1117,16 +1116,14 @@
           <t>Total,0
 Wang Hao23,0
 Lu Dinghao,100
-Lu Gongchao,0
-Xu Shirong,0</t>
+Lu Gongchao,100
+Xu Shirong,100</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>Total,0
-Wang Hao23,0
-Lu Gongchao,0
-Xu Shirong,0</t>
+Wang Hao23,0</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1134,8 +1131,8 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1251,16 +1248,14 @@
           <t>Total,0
 Wang Hao23,0
 Lu Dinghao,100
-Lu Gongchao,0
-Xu Shirong,0</t>
+Lu Gongchao,100
+Xu Shirong,100</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>Total,0
-Wang Hao23,0
-Lu Gongchao,0
-Xu Shirong,0</t>
+Wang Hao23,0</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1268,8 +1263,8 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1382,7 +1377,7 @@
 Tao Qichen,0
 Wang Hao23,100
 Lu Dinghao,100
-Xu Shirong,0
+Xu Shirong,100
 Zhao Kailiang,0</t>
         </is>
       </c>
@@ -1390,7 +1385,6 @@
         <is>
           <t>Total,0
 Tao Qichen,0
-Xu Shirong,0
 Zhao Kailiang,0</t>
         </is>
       </c>
@@ -1400,7 +1394,7 @@
 Tao Qichen,style="color:
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -1514,14 +1508,13 @@
 Tao Qichen,100
 Wang Hao23,100
 Lu Dinghao,100
-Xu Shirong,0
+Xu Shirong,100
 Zhao Kailiang,0</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>Total,0
-Xu Shirong,0
 Zhao Kailiang,0</t>
         </is>
       </c>
@@ -1531,7 +1524,7 @@
 Tao Qichen,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM8"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,12 +883,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30035089-EBP</t>
+          <t>30034747-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
+          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -904,7 +904,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SAIC-GM</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+          <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+          <t>Cheng Debao_程德宝(uched025)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -948,7 +948,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" s="1" t="n">
-        <v>46151</v>
+        <v>46158</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -963,11 +963,11 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" s="1" t="n">
-        <v>46186</v>
+        <v>46234</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -979,139 +979,6 @@
         </is>
       </c>
       <c r="AH4" t="inlineStr">
-        <is>
-          <t>Total,0
-Wang Hao23,0
-Lu Dinghao,100
-Xu Shirong,100
-Zhao Kailiang,0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Total,0
-Wang Hao23,0
-Zhao Kailiang,0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>未确认(cao liang)</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30034747-EBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Huawei Anhui</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Cheng Debao_程德宝(uched025)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" s="1" t="n">
-        <v>46158</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" s="1" t="n">
-        <v>46158</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" s="1" t="n">
-        <v>46165</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2027-09-30</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
         <is>
           <t>Total,0
 Wang Hao23,0
@@ -1120,422 +987,29 @@
 Xu Shirong,100</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>Total,0
 Wang Hao23,0</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Lu Gongchao,Submitted
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>未确认(cao liang)</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30034624-EBP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30034624-2026,AP,BYD,Lamination,260102,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>BYD</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" s="1" t="n">
-        <v>46158</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" s="1" t="n">
-        <v>46172</v>
-      </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2027-09-30</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Total,0
-Wang Hao23,0
-Lu Dinghao,100
-Lu Gongchao,100
-Xu Shirong,100</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Total,0
-Wang Hao23,0</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>未确认(cao liang)</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>30030290-EBP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>30030290-2027,AP,Mercedes-Benz,EU V530-IP, welding, 250266, T,Equipment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Min Hongen_闵宏恩(uminh009)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Phase 4 Manufacturing Development</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" s="1" t="n">
-        <v>45906</v>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" s="1" t="n">
-        <v>45920</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" s="1" t="n">
-        <v>45981</v>
-      </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" s="1" t="n">
-        <v>46157</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2027-09-30</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Total,0
-Tao Qichen,0
-Wang Hao23,100
-Lu Dinghao,100
-Xu Shirong,100
-Zhao Kailiang,0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Total,0
-Tao Qichen,0
-Zhao Kailiang,0</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Tao Qichen,style="color:
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>未确认(cao liang)</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>30030289-EBP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>30030289-2027,AP,Mercedes-Benz,EU V530-IP, welding, 250265, T,Equipment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Gao Yiheng01_高一恒(ugaoy160)</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Phase 4 Manufacturing Development</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" s="1" t="n">
-        <v>45906</v>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" s="1" t="n">
-        <v>45920</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" s="1" t="n">
-        <v>45948</v>
-      </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" s="1" t="n">
-        <v>46157</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2027-09-30</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Total,0
-Tao Qichen,100
-Wang Hao23,100
-Lu Dinghao,100
-Xu Shirong,100
-Zhao Kailiang,0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Total,0
-Zhao Kailiang,0</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Tao Qichen,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>未确认(cao liang)</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="n">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM4"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,12 +883,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30034747-EBP</t>
+          <t>30034746-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
+          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -948,26 +948,26 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" s="1" t="n">
-        <v>46158</v>
+        <v>46166</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" s="1" t="n">
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" s="1" t="n">
-        <v>46165</v>
+        <v>46179</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" s="1" t="n">
-        <v>46234</v>
+        <v>46221</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2027-09-30</t>
+          <t>2027-09-25</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -980,36 +980,1348 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Total,0
-Wang Hao23,0
-Lu Dinghao,100
-Lu Gongchao,100
-Xu Shirong,100</t>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Total,0
-Wang Hao23,0</t>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30034623-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2027-09-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30034480-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Phase0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30034479-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Phase0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30034478-EBP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30034478-2026,AP,Toyota,780B-DP, flaming,260080,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30034477-EBP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30033376-EBP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30033375-EBP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30033375-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260032，T,Equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>未确认(cao liang)</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>4</v>
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>30033373-EBP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30033373-2026,AP,Huawei Anhui,F03F05,Assembly,260030,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30032991-EBP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30032991-2026,AP,Jianghuai,JH-C-mirror,assembly,260009,14T,Equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30032988-EBP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30032988-2026,AP,SERES Motors,V32-mirror,Assembly,260007, 14T,Equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Guo Xinjie_郭新杰(uguox097)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -981,8 +981,8 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 </t>
@@ -990,17 +990,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
+          <t>Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Lu Gongchao,style="color:
 Xu Shirong,style="color:</t>
         </is>
@@ -1117,26 +1115,24 @@
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：0；
+Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
+          <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
-Lu Dinghao,style="color:
+Lu Dinghao,Submitted
 Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1246,7 +1242,7 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：0；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
@@ -1255,16 +1251,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+          <t>Lu Dinghao的PKR打分：0；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
 Lu Dinghao,style="color:
 Lu Gongchao,style="color:
 Xu Shirong,style="color:</t>
@@ -1377,8 +1372,8 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 </t>
@@ -1386,17 +1381,15 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
+          <t>Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Lu Gongchao,style="color:
 Xu Shirong,style="color:</t>
         </is>
@@ -1508,7 +1501,7 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；
@@ -1517,16 +1510,15 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+          <t>Lu Dinghao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
 Lu Dinghao,style="color:
 Xu Shirong,style="color:
 Zhao Kailiang,style="color:</t>
@@ -1639,8 +1631,8 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；
 </t>
@@ -1648,17 +1640,15 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+          <t>Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Xu Shirong,style="color:
 Zhao Kailiang,style="color:</t>
         </is>
@@ -1770,27 +1760,24 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -1903,15 +1890,14 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1919,7 +1905,7 @@
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -2032,15 +2018,14 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2048,7 +2033,7 @@
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -2159,27 +2144,24 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -2290,27 +2272,24 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP3"/>
+  <dimension ref="A1:AP7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,12 +631,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30035325-EBP</t>
+          <t>30033404-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30035325-2026,AP,SERES Motors,遮阳板,1200压机,260145,1M,Equipment</t>
+          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -656,7 +652,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SERES Motors</t>
+          <t>VW Group</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -666,10 +662,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -696,213 +696,832 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" s="1" t="n">
-        <v>46162</v>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" s="1" t="n">
-        <v>46164</v>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" s="1" t="n">
-        <v>46175</v>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF2" s="1" t="n">
-        <v>46387</v>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30033723-EBP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VW Group</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>未确认(Cao Liang)</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30033578-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Template-2 Self-made Tooling development program</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30035089-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30034166-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Template-3 Outsourcing management program</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>30034746-EBP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30035209-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>DFM</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Huawei Anhui</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Cheng Debao_程德宝(uched025)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Template-1 Self-made Equipment development program</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" s="1" t="n">
-        <v>46165</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" s="1" t="n">
-        <v>46179</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="AF3" s="1" t="n">
-        <v>46655</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2027-10-31</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
 Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP7"/>
+  <dimension ref="A1:AP5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,604 +738,6 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,style="color:
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>30033723-EBP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VW Group</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Wei Shaoguan_韦少官(uweis086)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Template-1 Self-made Equipment development program</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：100；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：100；
-</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,Submitted</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>未确认(Cao Liang)</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30033578-EBP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tes</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Phase 3 Design Feasibility</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Template-2 Self-made Tooling development program</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30035089-EBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SAIC-GM</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Phase 3 Design Feasibility</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Template-1 Self-made Equipment development program</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30034166-EBP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SAIC-GM</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Template-3 Outsourcing management program</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -1345,7 +747,7 @@
 </t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1354,174 +756,469 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30033578-EBP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Template-2 Self-made Tooling development program</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30034166-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Template-3 Outsourcing management program</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>30035209-EBP</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>DFM</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Jianghuai</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Template-1 Self-made Equipment development program</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr">
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>2027-10-31</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr">
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>Phase 2 Gate Exit-DVR</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -631,12 +631,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30033404-EBP</t>
+          <t>30034622-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
+          <t>30034622-2026,AP,BYD,Glue,260101,M,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -652,7 +652,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VW Group</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -662,15 +662,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -678,7 +682,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -698,7 +702,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -706,7 +710,7 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -714,19 +718,19 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -776,12 +780,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30033578-EBP</t>
+          <t>30034171-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -797,7 +801,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tes</t>
+          <t>Jianghuai</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -807,19 +811,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -847,7 +847,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -855,7 +855,7 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -863,19 +863,19 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -887,6 +887,304 @@
         </is>
       </c>
       <c r="AK3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30034168-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SVW</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Template-2 Self-made Tooling development program</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30034623-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2027-09-08</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -896,7 +1194,7 @@
 </t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -905,312 +1203,14 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30034166-EBP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SAIC-GM</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Template-3 Outsourcing management program</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：100；
-</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,Submitted</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>Lu Gongchao的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30035209-EBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Jianghuai</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Template-1 Self-made Equipment development program</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>2027-10-31</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP5"/>
+  <dimension ref="A1:AP8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,12 +631,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30034622-EBP</t>
+          <t>30034480-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30034622-2026,AP,BYD,Glue,260101,M,Equipment</t>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -652,7 +652,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -662,19 +662,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -682,7 +678,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -702,7 +698,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -710,7 +706,7 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -718,19 +714,19 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2027-09-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -738,7 +734,7 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Phase 4 Gate Exit-CPA</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -780,12 +776,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30034171-EBP</t>
+          <t>30034479-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -801,7 +797,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jianghuai</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -811,12 +807,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+          <t>Chen Jie04_陈洁(uchej018)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -838,7 +834,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Template-2 Self-made Tooling development program</t>
+          <t>Template-1 Self-made Equipment development program</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -847,7 +843,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -855,7 +851,7 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -863,19 +859,19 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -887,6 +883,151 @@
         </is>
       </c>
       <c r="AK3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30034478-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30034478-2026,AP,Toyota,780B-DP, flaming,260080,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -896,7 +1037,7 @@
 </t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -905,137 +1046,133 @@
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30034168-EBP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30034477-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>DFM</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SVW</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Template-2 Self-made Tooling development program</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -1045,7 +1182,7 @@
 </t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1054,137 +1191,137 @@
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30034623-EBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30034166-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>DFM</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BYD</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Template-1 Self-made Equipment development program</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>2027-09-08</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Template-3 Outsourcing management program</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -1194,7 +1331,7 @@
 </t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1203,22 +1340,320 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30035161-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30035162-EBP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP8"/>
+  <dimension ref="A1:AP25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,12 +631,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30034480-EBP</t>
+          <t>30028719-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
+          <t>30028719-2025,AP,smartmi,MX11-DAB,Lamination,250188,T,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -652,7 +652,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>smartmi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -662,15 +662,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Chen Ziyi01_陈子翌(uchez443)</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>Jin Yulong01_金宇隆(ujiny132)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Liu Cong02_刘聪(uliuc396)</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -678,7 +682,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -689,7 +693,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Template-1 Self-made Equipment development program</t>
+          <t>Template1 R&amp;D program</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -698,7 +702,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -706,7 +710,7 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -714,19 +718,19 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -734,7 +738,7 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -776,12 +780,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30034479-EBP</t>
+          <t>30032531-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
+          <t>30032531-2026,AP,SERES Motors,F2N-DAB, Lamination, 250383, T,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -797,7 +801,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>SERES Motors</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -807,15 +811,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -823,7 +831,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -834,16 +842,20 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Template-1 Self-made Equipment development program</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>Template-2(No DV phase or combined DV and PV)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>节点状态设置有问题，PM请更新</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -851,7 +863,7 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -859,19 +871,19 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -879,7 +891,7 @@
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -921,12 +933,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30034478-EBP</t>
+          <t>30033407-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30034478-2026,AP,Toyota,780B-DP, flaming,260080,T,Equipment</t>
+          <t>30033407-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260036,M,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -942,7 +954,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -952,15 +964,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Zhang Shuai27_张帅(uzhas1129)</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -968,7 +980,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -988,7 +1000,7 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -996,7 +1008,7 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1004,19 +1016,19 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -1024,7 +1036,7 @@
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1066,12 +1078,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30034477-EBP</t>
+          <t>30033376-EBP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1087,7 +1099,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1097,15 +1109,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -1113,7 +1125,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1124,7 +1136,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Template-1 Self-made Equipment development program</t>
+          <t>Template-2 Self-made Tooling development program</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -1133,7 +1145,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -1141,7 +1153,7 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1149,19 +1161,19 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
@@ -1169,7 +1181,7 @@
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1211,12 +1223,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30034166-EBP</t>
+          <t>30033405-EBP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+          <t>30033405-2026,AP,Huawei Anhui,F05 IP,Assembly,260038,M,Equipment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1232,7 +1244,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAIC-GM</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1242,14 +1254,10 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
-        </is>
-      </c>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
@@ -1262,7 +1270,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1273,7 +1281,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Template-3 Outsourcing management program</t>
+          <t>Template-1 Self-made Equipment development program</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1282,7 +1290,7 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1290,7 +1298,7 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1298,19 +1306,19 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -1318,10 +1326,1186 @@
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30033373-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30033373-2026,AP,Huawei Anhui,F03F05,Assembly,260030,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30033375-EBP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30033375-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260032，T,Equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30033409-EBP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30033409-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260037,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Template-2 Self-made Tooling development program</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30033723-EBP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VW Group</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30034473-EBP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30034473-2026,AP,SERES Motors,F2N-light,260081,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>30032706-EBP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30032706-2025,AP,SERES Motors,A15-mirror, assy, 260006, 15T,Equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Wang Wanfang_王万芳(uwanw356)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Template-2(No DV phase or combined DV and PV)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30033461-EBP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30033461-2026,AP,SVW,B-SUV-mirror,assy,260041,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SVW</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Template-3 Outsourcing management program</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30034615-EBP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30034615-2026,AP,BYD,MR&amp;ST-IP, Glue,260091, M,Equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Yuan Shuai_袁帅(uyuas003)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -1331,7 +2515,7 @@
 </t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1340,137 +2524,278 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AM14" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AN14" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>30035161-EBP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>30030761-EBP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30030761-2025,AP,SAIC-VW,VW416-IP,Automatin,250306,M,,Equipment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>DFM</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>BJEV</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SAIC-VW</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Liu Jinghua01_刘璟华(uliuj595)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Template1 R&amp;D program</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>30035325-EBP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>30035325-2026,AP,SERES Motors,遮阳板,1200压机,260145,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Template-1 Self-made Equipment development program</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>2027-10-20</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -1480,7 +2805,7 @@
 </t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1489,137 +2814,137 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AM16" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AN16" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>30035162-EBP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>30035205-EBP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30035205-2027,AP,SERES Motors,E68-DP,lamination,260138,2M,Equipment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>DFM</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BJEV</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Yuan Shuai_袁帅(uyuas003)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>Template-1 Self-made Equipment development program</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>2027-10-20</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>Phase 2 Gate Exit-DVR</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AK17" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -1629,7 +2954,7 @@
 </t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1638,22 +2963,1210 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AM17" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AN17" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>30035209-EBP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>2027-10-31</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>30017341-EBP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>30017341-2024,AP,BYD,SA5-IP,Lamination,220281,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Liu Cong02_刘聪(uliuc396)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>30034578-EBP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>30034578-2026,AP,BYD,Glue,260093,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>30035208-EBP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>30035208-2026,AP,Jianghuai,C673-DP,Foam Sticking,260140,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>2027-10-29</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>30034577-EBP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>30034577-2026,AP,BYD,EHX,Glue,260088,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>30035188-EBP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30035188-2026,AP,smartmi,KUNLUN-light,welding.260135.M,Equipment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>smartmi</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>30035096-EBP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30035096-2026,AP,smartmi,F2N-light,welding260130,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>smartmi</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>30035161-EBP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP8"/>
+  <dimension ref="A1:AP9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,12 +631,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30034579-EBP</t>
+          <t>30034171-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30034579-2026,AP,BYD,Glue,260095,M,Equipment</t>
+          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -652,7 +652,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Jianghuai</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -693,7 +693,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Template-1 Self-made Equipment development program</t>
+          <t>Template-2 Self-made Tooling development program</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -702,7 +702,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -710,7 +710,7 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -718,19 +718,19 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -738,26 +738,26 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
+Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,Submitted
+Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,Submitted</t>
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -767,7 +767,9 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>Lu Gongchao的PKR打分：0；</t>
+          <t>Wang Hao23的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -780,12 +782,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30035236-EBP</t>
+          <t>30034168-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30035236-2026,NA,Ford,P703-Airbag, assembly, 260142,1T,Equipment</t>
+          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -793,11 +795,15 @@
           <t>DFM</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>SVW</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -812,10 +818,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Huang Dinghui_黄定辉(uhuad002)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -823,7 +833,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -834,7 +844,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Template-3 Outsourcing management program</t>
+          <t>Template-2 Self-made Tooling development program</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -843,7 +853,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -851,7 +861,7 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -859,19 +869,19 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -879,7 +889,7 @@
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -887,7 +897,7 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：100；
+Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
@@ -897,7 +907,7 @@
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,Submitted
+Xu Shirong,style="color:
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -908,7 +918,8 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Zhao Kailiang的PKR打分：0；</t>
+          <t>Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -921,12 +932,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30036184-EBP</t>
+          <t>30034746-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30036184-2026,AP,JAC-VW,JHB-sunvisor,assem, 260180, 2T,Equipment</t>
+          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -942,7 +953,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JAC-VW</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -950,10 +961,14 @@
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+          <t>Cheng Debao_程德宝(uched025)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,7 +983,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -979,7 +994,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Template-2 Self-made Tooling development program</t>
+          <t>Template-1 Self-made Equipment development program</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -988,7 +1003,7 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -996,7 +1011,7 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1004,19 +1019,19 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-09-25</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -1024,26 +1039,26 @@
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1053,15 +1068,13 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>下周</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr"/>
@@ -1069,12 +1082,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30033911-EBP</t>
+          <t>30035162-EBP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
+          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1082,11 +1095,15 @@
           <t>DFM</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>BJEV</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1094,10 +1111,14 @@
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Jin Yulong01_金宇隆(ujiny132)</t>
+          <t>Chen Jie04_陈洁(uchej018)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1112,7 +1133,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1123,7 +1144,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Template-3 Outsourcing management program</t>
+          <t>Template-1 Self-made Equipment development program</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -1132,7 +1153,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -1140,7 +1161,7 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1148,19 +1169,19 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-10-20</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
@@ -1168,18 +1189,26 @@
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Phase 4 Gate Exit-CPA</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：；
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Total,style="color:</t>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1189,12 +1218,14 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>Wang Hao23的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>下周</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr"/>
@@ -1227,7 +1258,11 @@
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Jin Yulong01_金宇隆(ujiny132)</t>
@@ -1306,18 +1341,26 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：；
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Total,style="color:</t>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>未评分(工程师)</t>
+          <t>未确认(Cao Liang)</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -1335,12 +1378,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30036039-EBP</t>
+          <t>30033911-EBP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30036039-2026,AP,SERES Motors,L97-DAB, Lamination, 260171, 1T,Equipment</t>
+          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1348,15 +1391,11 @@
           <t>DFM</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SERES Motors</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1364,10 +1403,14 @@
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+          <t>Jin Yulong01_金宇隆(ujiny132)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1393,7 +1436,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Template-2 Self-made Tooling development program</t>
+          <t>Template-3 Outsourcing management program</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1402,7 +1445,7 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1410,7 +1453,7 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1425,12 +1468,12 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr"/>
@@ -1438,18 +1481,26 @@
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：；
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Total,style="color:</t>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1459,7 +1510,9 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>Wang Hao23的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1472,12 +1525,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30035707-EBP</t>
+          <t>30036039-EBP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30035707-2026,AP,Brilliance-BMW,RGB 8PIN-light,assemble,260156,T,Equipment</t>
+          <t>30036039-2026,AP,SERES Motors,L97-DAB, Lamination, 260171, 1T,Equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1493,7 +1546,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brilliance-BMW</t>
+          <t>SERES Motors</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1503,12 +1556,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
+          <t>Huang Dongfang01_黄东方(uhuad056)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1534,7 +1587,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Template-1 Self-made Equipment development program</t>
+          <t>Template-2 Self-made Tooling development program</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1543,7 +1596,7 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1551,7 +1604,7 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1559,19 +1612,19 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr"/>
@@ -1584,11 +1637,11 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：0；
+          <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
 Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
@@ -1597,26 +1650,177 @@
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,Submitted
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>未确认(Cao Liang)</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30035707-EBP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30035707-2026,AP,Brilliance-BMW,RGB 8PIN-light,assemble,260156,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Brilliance-BMW</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>本周</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -631,12 +631,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30034171-EBP</t>
+          <t>30030313-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
+          <t>30030313-2026,AP,Tes,Highland-FC,Assembly,250268,3T,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -652,7 +652,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jianghuai</t>
+          <t>Tes</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -662,17 +662,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+          <t>Li Yanchen_李彦辰(ulixy466)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+          <t>Zhou Meijiao01_周美娇(uzhom121)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -693,7 +693,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Template-2 Self-made Tooling development program</t>
+          <t>Template1 R&amp;D program</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -702,7 +702,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -710,7 +710,7 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -718,19 +718,19 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -738,7 +738,7 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Phase 4 Gate Exit-CPA</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -746,8 +746,8 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
@@ -756,8 +756,8 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -767,9 +767,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Wang Hao23的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -777,17 +775,21 @@
           <t>下周</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Gongchao.Lu@yanfeng.com; Hao.Wang23@yanfeng.com; Shirong.Xu@yanfeng.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30034168-EBP</t>
+          <t>30034171-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
+          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -803,7 +805,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SVW</t>
+          <t>Jianghuai</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -818,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -833,7 +835,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -881,7 +883,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -895,20 +897,20 @@
       <c r="AK3" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
+Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,Submitted
+Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -918,13 +920,12 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Wang Hao23的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>下周</t>
+          <t>本周</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr"/>
@@ -932,12 +933,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30034746-EBP</t>
+          <t>30034480-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -953,7 +954,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Huawei Anhui</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -963,19 +964,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cheng Debao_程德宝(uched025)</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -1003,7 +1000,7 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -1011,7 +1008,7 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1019,19 +1016,19 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2027-09-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -1043,156 +1040,6 @@
         </is>
       </c>
       <c r="AK4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30035162-EBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BJEV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Template-1 Self-made Equipment development program</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>2027-10-20</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：0；
@@ -1202,7 +1049,7 @@
 </t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,style="color:
@@ -1211,280 +1058,135 @@
 Xu Shirong,style="color:</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>Wang Hao23的PKR打分：0；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30033911-EBP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30034479-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>DFM</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Wang Xiang02_王翔(uwanx029)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Jin Yulong01_金宇隆(ujiny132)</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Template-3 Outsourcing management program</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：100；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：100；
-Xu Shirong的PKR打分：100；
-</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>未确认(Cao Liang)</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>30033911-EBP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DFM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Wang Xiang02_王翔(uwanx029)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Jin Yulong01_金宇隆(ujiny132)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Template-3 Outsourcing management program</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：0；
@@ -1494,7 +1196,7 @@
 </t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,style="color:
@@ -1503,16 +1205,311 @@
 Xu Shirong,style="color:</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>Wang Hao23的PKR打分：0；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30034477-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30035162-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1525,12 +1522,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30036039-EBP</t>
+          <t>30036184-EBP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30036039-2026,AP,SERES Motors,L97-DAB, Lamination, 260171, 1T,Equipment</t>
+          <t>30036184-2026,AP,JAC-VW,JHB-sunvisor,assem, 260180, 2T,Equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1546,7 +1543,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SERES Motors</t>
+          <t>JAC-VW</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1556,12 +1553,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1576,7 +1573,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1596,7 +1593,7 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1604,7 +1601,7 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1612,19 +1609,19 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr"/>
@@ -1632,41 +1629,42 @@
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：100；
-Wang Hao23的PKR打分：100；
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：100；
-Xu Shirong的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,Submitted
+Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
+Xu Shirong,style="color:
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>未确认(Cao Liang)</t>
+          <t>未评分(工程师)</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>Wang Hao23的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>下周</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr"/>
@@ -1789,8 +1787,8 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
@@ -1799,8 +1797,8 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1810,9 +1808,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Wang Hao23的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">

--- a/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
+++ b/yanfeng/PKR确认信息/PKR历史未完成记录.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP9"/>
+  <dimension ref="A1:AP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,12 +631,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30030313-EBP</t>
+          <t>30028728-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30030313-2026,AP,Tes,Highland-FC,Assembly,250268,3T,Equipment</t>
+          <t>30028728-2025,AP,smartmi,MX11-DAB,Lamination.250190,T,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -652,7 +652,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tes</t>
+          <t>smartmi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -662,17 +662,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Li Yanchen_李彦辰(ulixy466)</t>
+          <t>Guo Xinjie_郭新杰(uguox097)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Zhou Meijiao01_周美娇(uzhom121)</t>
+          <t>Liu Cong02_刘聪(uliuc396)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -702,7 +702,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -710,7 +710,7 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -718,19 +718,19 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -744,20 +744,20 @@
       <c r="AK2" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,Submitted</t>
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；</t>
+          <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -775,21 +775,17 @@
           <t>下周</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Gongchao.Lu@yanfeng.com; Hao.Wang23@yanfeng.com; Shirong.Xu@yanfeng.com</t>
-        </is>
-      </c>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30034171-EBP</t>
+          <t>30033409-EBP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
+          <t>30033409-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260037,M,Equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -805,7 +801,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jianghuai</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -815,12 +811,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+          <t>Feng Quanhua_冯全华(ufenq022)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,7 +851,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -863,7 +859,7 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -871,19 +867,19 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -897,8 +893,8 @@
       <c r="AK3" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
 Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：100；
 </t>
@@ -907,8 +903,8 @@
       <c r="AL3" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
 Xu Shirong,Submitted
 Zhao Kailiang,Submitted</t>
         </is>
@@ -920,12 +916,12 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；</t>
+          <t>Lu Dinghao的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>下周</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr"/>
@@ -933,12 +929,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30034480-EBP</t>
+          <t>30034615-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
+          <t>30034615-2026,AP,BYD,MR&amp;ST-IP, Glue,260091, M,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +950,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -964,15 +960,19 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Yuan Shuai_袁帅(uyuas003)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Chen Ziyi01_陈子翌(uchez443)</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -980,7 +980,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1016,19 +1016,19 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -1042,20 +1042,20 @@
       <c r="AK4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1065,9 +1065,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
+          <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1080,12 +1078,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30034479-EBP</t>
+          <t>30030761-EBP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
+          <t>30030761-2025,AP,SAIC-VW,VW416-IP,Automatin,250306,M,,Equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1101,7 +1099,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>SAIC-VW</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1111,15 +1109,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Xia Yang_夏阳(uxiay057)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Liu Jinghua01_刘璟华(uliuj595)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -1127,7 +1129,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1138,7 +1140,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Template-1 Self-made Equipment development program</t>
+          <t>Template1 R&amp;D program</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -1147,7 +1149,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -1155,7 +1157,7 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1163,19 +1165,19 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
@@ -1188,33 +1190,31 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>未评分(工程师)</t>
+          <t>未确认(Cao Liang)</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30034477-EBP</t>
+          <t>30033461-EBP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+          <t>30033461-2026,AP,SVW,B-SUV-mirror,assy,260041,1M,Equipment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>SVW</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1258,15 +1258,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
@@ -1274,7 +1278,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1285,7 +1289,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Template-1 Self-made Equipment development program</t>
+          <t>Template-3 Outsourcing management program</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1294,7 +1298,7 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1302,7 +1306,7 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1310,19 +1314,19 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -1336,9 +1340,9 @@
       <c r="AK6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：100；
 </t>
         </is>
@@ -1346,9 +1350,9 @@
       <c r="AL6" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,Submitted</t>
         </is>
       </c>
@@ -1359,8 +1363,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
+          <t>Lu Dinghao的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1373,12 +1376,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30035162-EBP</t>
+          <t>30031540-EBP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
+          <t>30031540-2026,AP,Huawei Anhui,EHV-DP,Lamination,250339,T,Equipment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1394,7 +1397,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BJEV</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1404,12 +1407,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Xia Yang_夏阳(uxiay057)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1424,7 +1427,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1435,7 +1438,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Template-1 Self-made Equipment development program</t>
+          <t>Template2 Standard Program, Standard equipment/Tooling development program</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1444,7 +1447,7 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1452,7 +1455,7 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1460,7 +1463,7 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1472,7 +1475,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2027-10-20</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr"/>
@@ -1480,15 +1483,15 @@
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：100；
 </t>
         </is>
@@ -1496,9 +1499,9 @@
       <c r="AL7" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Lu Gongchao,Submitted
+Lu Gongchao,style="color:
 Xu Shirong,Submitted</t>
         </is>
       </c>
@@ -1509,12 +1512,12 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；</t>
+          <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>下周</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr"/>
@@ -1522,12 +1525,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30036184-EBP</t>
+          <t>30034624-EBP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30036184-2026,AP,JAC-VW,JHB-sunvisor,assem, 260180, 2T,Equipment</t>
+          <t>30034624-2026,AP,BYD,Lamination,260102,M,Equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1543,7 +1546,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JAC-VW</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1553,12 +1556,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
+          <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1573,7 +1576,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1584,7 +1587,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Template-2 Self-made Tooling development program</t>
+          <t>Template-1 Self-made Equipment development program</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1593,7 +1596,7 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1601,7 +1604,7 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1609,19 +1612,19 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr"/>
@@ -1629,26 +1632,26 @@
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,Submitted</t>
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1658,8 +1661,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
+          <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1672,12 +1674,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30035707-EBP</t>
+          <t>30034747-EBP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30035707-2026,AP,Brilliance-BMW,RGB 8PIN-light,assemble,260156,T,Equipment</t>
+          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1693,7 +1695,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brilliance-BMW</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1703,12 +1705,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+          <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
+          <t>Cheng Debao_程德宝(uched025)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1723,7 +1725,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1743,7 +1745,7 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1751,7 +1753,7 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1759,19 +1761,19 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr"/>
@@ -1779,44 +1781,1384 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30034166-EBP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Template-3 Outsourcing management program</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30035205-EBP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30035205-2027,AP,SERES Motors,E68-DP,lamination,260138,2M,Equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yuan Shuai_袁帅(uyuas003)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>30033043-EBP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30033043-2027,AP,General Motors,C1UL-IP,Lamination,260020,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Guo Zhengyang_郭正阳(uguoz023)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Gao Yiheng01_高一恒(ugaoy160)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30035208-EBP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30035208-2026,AP,Jianghuai,C673-DP,Foam Sticking,260140,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>2027-10-29</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30035161-EBP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>30035162-EBP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>30035945-EBP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>30035945-2027,NA,Toyota,815/825D-OHC, assy, 260168, 2M,Equipment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>2027-10-31</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
 Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Xu Shirong,Submitted
 Zhao Kailiang,Submitted</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>未确认(Cao Liang)</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>30036039-EBP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30036039-2026,AP,SERES Motors,L97-DAB, Lamination, 260171, 1T,Equipment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Template-2 Self-made Tooling development program</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr"/>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>30035707-EBP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30035707-2026,AP,Brilliance-BMW,RGB 8PIN-light,assemble,260156,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DFM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brilliance-BMW</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Template-1 Self-made Equipment development program</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
